--- a/ModExample/Defs/excel_data/箱子.xlsx
+++ b/ModExample/Defs/excel_data/箱子.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Territory\数值表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB19FD4E-E02D-4A06-8CA9-C2BD63F6C3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CE8C9E-681A-4D02-8F29-FC0F3004C366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3540" yWindow="2820" windowWidth="23835" windowHeight="11580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="28830" windowHeight="15510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="box" sheetId="1" r:id="rId1"/>
@@ -1492,7 +1492,7 @@
         <v>29</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>61</v>
